--- a/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>20.1</v>
+      <c r="D5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7">
-        <v>21.2</v>
+      <c r="D7" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>21.6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>21.4</v>
+      <c r="D12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>21.6</v>
+      <c r="D14" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>21.3</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>20.7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>20.9</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>20.1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -694,7 +694,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1001,8 +1001,8 @@
       <c r="C44">
         <v>12</v>
       </c>
-      <c r="D44" t="s">
-        <v>4</v>
+      <c r="D44">
+        <v>20.9</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1029,8 +1029,8 @@
       <c r="C46">
         <v>14</v>
       </c>
-      <c r="D46" t="s">
-        <v>4</v>
+      <c r="D46">
+        <v>18.9</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1170,7 +1170,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>19</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="57" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Dry_bulb_temp_06h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -455,8 +452,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>20.1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -483,8 +480,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>21.2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -540,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -553,8 +550,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>21.2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -581,8 +578,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>21.6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -609,8 +606,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>21.3</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -680,7 +677,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>20.1</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -694,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1057,8 +1054,8 @@
       <c r="C48">
         <v>16</v>
       </c>
-      <c r="D48" t="s">
-        <v>4</v>
+      <c r="D48">
+        <v>19.8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1071,8 +1068,8 @@
       <c r="C49">
         <v>17</v>
       </c>
-      <c r="D49" t="s">
-        <v>4</v>
+      <c r="D49">
+        <v>20.6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1099,8 +1096,8 @@
       <c r="C51">
         <v>19</v>
       </c>
-      <c r="D51" t="s">
-        <v>4</v>
+      <c r="D51">
+        <v>20.1</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1170,7 +1167,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>11.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="57" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Dry_bulb_temp_06h00</t>
+  </si>
+  <si>
+    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -550,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>21.2</v>
+      <c r="D12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -606,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>21.3</v>
+      <c r="D16" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1167,7 +1170,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Dry_bulb_temp_06h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -553,8 +550,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>21.2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -609,8 +606,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>21.3</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1170,7 +1167,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>19</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="57" spans="1:4">
